--- a/Data/equipes.xlsx
+++ b/Data/equipes.xlsx
@@ -32,9 +32,6 @@
   </x:si>
   <x:si>
     <x:t>Nom</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-2027</x:t>
   </x:si>
   <x:si>
     <x:t>FootballAmericain</x:t>
@@ -434,16 +431,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="D2" s="0" t="s">
+      <x:c r="E2" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
-      <x:c r="E2" s="0" t="s">
+      <x:c r="F2" s="0" t="s">
         <x:v>8</x:v>
-      </x:c>
-      <x:c r="F2" s="0" t="s">
-        <x:v>9</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:6">
@@ -454,16 +451,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
         <x:v>10</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
+      <x:c r="F3" s="0" t="s">
         <x:v>11</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Data/equipes.xlsx
+++ b/Data/equipes.xlsx
@@ -34,22 +34,43 @@
     <x:t>Nom</x:t>
   </x:si>
   <x:si>
+    <x:t>2025-2026</x:t>
+  </x:si>
+  <x:si>
     <x:t>FootballAmericain</x:t>
   </x:si>
   <x:si>
     <x:t>Benjamin</x:t>
   </x:si>
   <x:si>
-    <x:t>Les Aigles de l'Amitié</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2025-2026</x:t>
+    <x:t>Les Aigles — Football — Benjamin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>true</x:t>
   </x:si>
   <x:si>
     <x:t>Cadet</x:t>
   </x:si>
   <x:si>
-    <x:t>Les aigles de l'Amitié</x:t>
+    <x:t>Les Aigles — Football — Cadet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>false</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Les Scorpions — Football — Benjamin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-2027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hockey</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Atome</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Les Aigles — Hockey — Atome</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -403,7 +424,7 @@
   <x:dimension ref="A1:F1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:6">
+    <x:row r="1" spans="1:7">
       <x:c r="A1" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -423,44 +444,119 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:6">
+    <x:row r="2" spans="1:7">
       <x:c r="A2" s="0">
-        <x:v>1</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B2" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="D2" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="E2" s="0" t="s">
+      <x:c r="G2" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:7">
+      <x:c r="A3" s="0">
         <x:v>7</x:v>
-      </x:c>
-      <x:c r="F2" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:6">
-      <x:c r="A3" s="0">
-        <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:7">
+      <x:c r="A4" s="0">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B4" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:7">
+      <x:c r="A5" s="0">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s">
+      <x:c r="B5" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:7">
+      <x:c r="A6" s="0">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B6" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
         <x:v>6</x:v>
       </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>11</x:v>
+      <x:c r="D6" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>13</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Data/equipes.xlsx
+++ b/Data/equipes.xlsx
@@ -61,16 +61,13 @@
     <x:t>Les Scorpions — Football — Benjamin</x:t>
   </x:si>
   <x:si>
+    <x:t>Juvenil</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Les Aigles — Football — Juvénile</x:t>
+  </x:si>
+  <x:si>
     <x:t>2026-2027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hockey</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Atome</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Les Aigles — Hockey — Atome</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -521,16 +518,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>7</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
         <x:v>13</x:v>
@@ -544,16 +541,16 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
         <x:v>13</x:v>

--- a/Data/equipes.xlsx
+++ b/Data/equipes.xlsx
@@ -55,19 +55,31 @@
     <x:t>Les Aigles — Football — Cadet</x:t>
   </x:si>
   <x:si>
+    <x:t>Les Scorpions — Football — Benjamin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Juvenil</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Les Aigles — Football — Juvénile</x:t>
+  </x:si>
+  <x:si>
     <x:t>false</x:t>
   </x:si>
   <x:si>
-    <x:t>Les Scorpions — Football — Benjamin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Juvenil</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Les Aigles — Football — Juvénile</x:t>
-  </x:si>
-  <x:si>
     <x:t>2026-2027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Les Scorpions — Football — Cadet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hockey</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Atome</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Les Aigles — Hockey — Atome</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -484,7 +496,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>10</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:7">
@@ -504,7 +516,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
         <x:v>10</x:v>
@@ -524,13 +536,13 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="F5" s="0" t="s">
+      <x:c r="G5" s="0" t="s">
         <x:v>16</x:v>
-      </x:c>
-      <x:c r="G5" s="0" t="s">
-        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:7">
@@ -553,7 +565,53 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:7">
+      <x:c r="A7" s="0">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B7" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:7">
+      <x:c r="A8" s="0">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B8" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>16</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Data/equipes.xlsx
+++ b/Data/equipes.xlsx
@@ -34,6 +34,9 @@
     <x:t>Nom</x:t>
   </x:si>
   <x:si>
+    <x:t>AfficherPublic</x:t>
+  </x:si>
+  <x:si>
     <x:t>2025-2026</x:t>
   </x:si>
   <x:si>
@@ -47,39 +50,6 @@
   </x:si>
   <x:si>
     <x:t>true</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cadet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Les Aigles — Football — Cadet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Les Scorpions — Football — Benjamin</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Juvenil</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Les Aigles — Football — Juvénile</x:t>
-  </x:si>
-  <x:si>
-    <x:t>false</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-2027</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Les Scorpions — Football — Cadet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Hockey</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Atome</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Les Aigles — Hockey — Atome</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -430,7 +400,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:F1"/>
+  <x:dimension ref="A1:G1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:7">
@@ -452,166 +422,31 @@
       <x:c r="F1" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
+      <x:c r="G1" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" spans="1:7">
       <x:c r="A2" s="0">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:7">
-      <x:c r="A3" s="0">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B3" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
         <x:v>11</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:7">
-      <x:c r="A4" s="0">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B4" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:7">
-      <x:c r="A5" s="0">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B5" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F5" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G5" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:7">
-      <x:c r="A6" s="0">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B6" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="G6" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:7">
-      <x:c r="A7" s="0">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B7" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G7" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:7">
-      <x:c r="A8" s="0">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B8" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F8" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="G8" s="0" t="s">
-        <x:v>16</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Data/equipes.xlsx
+++ b/Data/equipes.xlsx
@@ -50,6 +50,18 @@
   </x:si>
   <x:si>
     <x:t>true</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cadet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Les Aigles — Football — Cadet</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -403,7 +415,7 @@
   <x:dimension ref="A1:G1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:7">
+    <x:row r="1" spans="1:8">
       <x:c r="A1" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -426,7 +438,7 @@
         <x:v>6</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:7">
+    <x:row r="2" spans="1:8">
       <x:c r="A2" s="0">
         <x:v>1</x:v>
       </x:c>
@@ -447,6 +459,35 @@
       </x:c>
       <x:c r="G2" s="0" t="s">
         <x:v>11</x:v>
+      </x:c>
+      <x:c r="H2" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:8">
+      <x:c r="A3" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>15</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Data/equipes.xlsx
+++ b/Data/equipes.xlsx
@@ -37,6 +37,9 @@
     <x:t>AfficherPublic</x:t>
   </x:si>
   <x:si>
+    <x:t>ThemeId</x:t>
+  </x:si>
+  <x:si>
     <x:t>2025-2026</x:t>
   </x:si>
   <x:si>
@@ -61,7 +64,19 @@
     <x:t>Les Aigles — Football — Cadet</x:t>
   </x:si>
   <x:si>
+    <x:t>false</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Juvenil</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cheerleader des aigles — Football — Juvénile</x:t>
+  </x:si>
+  <x:si>
     <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-2027</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -412,7 +427,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G1"/>
+  <x:dimension ref="A1:H1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:8">
@@ -437,6 +452,9 @@
       <x:c r="G1" s="0" t="s">
         <x:v>6</x:v>
       </x:c>
+      <x:c r="H1" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" spans="1:8">
       <x:c r="A2" s="0">
@@ -446,22 +464,22 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8">
@@ -472,22 +490,74 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:8">
+      <x:c r="A4" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B4" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="E3" s="0" t="s">
+      <x:c r="D4" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:8">
+      <x:c r="A5" s="0">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B5" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="H3" s="0" t="s">
-        <x:v>15</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Data/equipes.xlsx
+++ b/Data/equipes.xlsx
@@ -49,34 +49,13 @@
     <x:t>Benjamin</x:t>
   </x:si>
   <x:si>
-    <x:t>Les Aigles — Football — Benjamin</x:t>
-  </x:si>
-  <x:si>
     <x:t>true</x:t>
   </x:si>
   <x:si>
     <x:t>1</x:t>
   </x:si>
   <x:si>
-    <x:t>Cadet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Les Aigles — Football — Cadet</x:t>
-  </x:si>
-  <x:si>
-    <x:t>false</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Juvenil</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cheerleader des aigles — Football — Juvénile</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-2027</x:t>
+    <x:t>01fd121d-dd01-4cc1-9d38-7d9bc159d6aa</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -430,7 +409,7 @@
   <x:dimension ref="A1:H1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:8">
+    <x:row r="1" spans="1:9">
       <x:c r="A1" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -456,7 +435,7 @@
         <x:v>7</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:8">
+    <x:row r="2" spans="1:9">
       <x:c r="A2" s="0">
         <x:v>1</x:v>
       </x:c>
@@ -473,90 +452,15 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="G2" s="0" t="s">
+      <x:c r="H2" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="H2" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:8">
-      <x:c r="A3" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B3" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H3" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:8">
-      <x:c r="A4" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B4" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="H4" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:8">
-      <x:c r="A5" s="0">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B5" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="F5" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="G5" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="H5" s="0" t="s">
+      <x:c r="I2" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
     </x:row>
